--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743281</v>
       </c>
       <c r="B2" t="n">
-        <v>90936</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122743278</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743281</v>
+        <v>122743278</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492932</v>
+        <v>492771</v>
       </c>
       <c r="R2" t="n">
-        <v>7144160</v>
+        <v>7144199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743278</v>
+        <v>122743281</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492771</v>
+        <v>492932</v>
       </c>
       <c r="R3" t="n">
-        <v>7144199</v>
+        <v>7144160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743278</v>
+        <v>122743281</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492771</v>
+        <v>492932</v>
       </c>
       <c r="R2" t="n">
-        <v>7144199</v>
+        <v>7144160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743281</v>
+        <v>122743278</v>
       </c>
       <c r="B3" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492932</v>
+        <v>492771</v>
       </c>
       <c r="R3" t="n">
-        <v>7144160</v>
+        <v>7144199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743281</v>
+        <v>122743278</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492932</v>
+        <v>492771</v>
       </c>
       <c r="R2" t="n">
-        <v>7144160</v>
+        <v>7144199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743278</v>
+        <v>122743281</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492771</v>
+        <v>492932</v>
       </c>
       <c r="R3" t="n">
-        <v>7144199</v>
+        <v>7144160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743281</v>
+        <v>122743278</v>
       </c>
       <c r="B2" t="n">
-        <v>90948</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492932</v>
+        <v>492771</v>
       </c>
       <c r="R2" t="n">
-        <v>7144160</v>
+        <v>7144199</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743278</v>
+        <v>122743281</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>90951</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492771</v>
+        <v>492932</v>
       </c>
       <c r="R3" t="n">
-        <v>7144199</v>
+        <v>7144160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743278</v>
+        <v>122743281</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>90953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492771</v>
+        <v>492932</v>
       </c>
       <c r="R2" t="n">
-        <v>7144199</v>
+        <v>7144160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743281</v>
+        <v>122743278</v>
       </c>
       <c r="B3" t="n">
-        <v>90951</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492932</v>
+        <v>492771</v>
       </c>
       <c r="R3" t="n">
-        <v>7144160</v>
+        <v>7144199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127028941</v>
+        <v>127029146</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>80115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492956</v>
+        <v>493010</v>
       </c>
       <c r="R4" t="n">
-        <v>7144106</v>
+        <v>7144126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029146</v>
+        <v>127028941</v>
       </c>
       <c r="B5" t="n">
-        <v>80084</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493010</v>
+        <v>492956</v>
       </c>
       <c r="R5" t="n">
-        <v>7144126</v>
+        <v>7144106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
         <v>127028985</v>
       </c>
       <c r="B6" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127029012</v>
       </c>
       <c r="B7" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127029103</v>
       </c>
       <c r="B9" t="n">
-        <v>79061</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>127029404</v>
       </c>
       <c r="B10" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029146</v>
+        <v>127028941</v>
       </c>
       <c r="B4" t="n">
-        <v>80115</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493010</v>
+        <v>492956</v>
       </c>
       <c r="R4" t="n">
-        <v>7144126</v>
+        <v>7144106</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127028941</v>
+        <v>127029146</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>80118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492956</v>
+        <v>493010</v>
       </c>
       <c r="R5" t="n">
-        <v>7144106</v>
+        <v>7144126</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
         <v>127028985</v>
       </c>
       <c r="B6" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127029012</v>
       </c>
       <c r="B7" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127029103</v>
       </c>
       <c r="B9" t="n">
-        <v>79092</v>
+        <v>79095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>127029404</v>
       </c>
       <c r="B10" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127028941</v>
+        <v>127029146</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>80118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492956</v>
+        <v>493010</v>
       </c>
       <c r="R4" t="n">
-        <v>7144106</v>
+        <v>7144126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029146</v>
+        <v>127028941</v>
       </c>
       <c r="B5" t="n">
-        <v>80118</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493010</v>
+        <v>492956</v>
       </c>
       <c r="R5" t="n">
-        <v>7144126</v>
+        <v>7144106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>127029146</v>
       </c>
       <c r="B4" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127028941</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>127028985</v>
       </c>
       <c r="B6" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127029012</v>
       </c>
       <c r="B7" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127029103</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>127029404</v>
       </c>
       <c r="B10" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029146</v>
+        <v>127028941</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493010</v>
+        <v>492956</v>
       </c>
       <c r="R4" t="n">
-        <v>7144126</v>
+        <v>7144106</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127028941</v>
+        <v>127029146</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492956</v>
+        <v>493010</v>
       </c>
       <c r="R5" t="n">
-        <v>7144106</v>
+        <v>7144126</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>127028941</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127029146</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>127028985</v>
       </c>
       <c r="B6" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127029012</v>
       </c>
       <c r="B7" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127029103</v>
       </c>
       <c r="B9" t="n">
-        <v>79099</v>
+        <v>79101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>127029404</v>
       </c>
       <c r="B10" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127028941</v>
+        <v>127029146</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>80124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492956</v>
+        <v>493010</v>
       </c>
       <c r="R4" t="n">
-        <v>7144106</v>
+        <v>7144126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029146</v>
+        <v>127028941</v>
       </c>
       <c r="B5" t="n">
-        <v>80124</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493010</v>
+        <v>492956</v>
       </c>
       <c r="R5" t="n">
-        <v>7144126</v>
+        <v>7144106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>127029146</v>
       </c>
       <c r="B4" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127028941</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>127028985</v>
       </c>
       <c r="B6" t="n">
-        <v>82861</v>
+        <v>82852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127029012</v>
       </c>
       <c r="B7" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>127029337</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127029103</v>
       </c>
       <c r="B9" t="n">
-        <v>79101</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>127029404</v>
       </c>
       <c r="B10" t="n">
-        <v>82861</v>
+        <v>82852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743281</v>
+        <v>127029103</v>
       </c>
       <c r="B2" t="n">
-        <v>91913</v>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräningen SÖ, Jmt</t>
+          <t>Skiddammtjärnen, Skiddammtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492932</v>
+        <v>492989</v>
       </c>
       <c r="R2" t="n">
-        <v>7144160</v>
+        <v>7144133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,33 +754,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles, gammal grannaturskog/gransumpskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743278</v>
+        <v>122743281</v>
       </c>
       <c r="B3" t="n">
-        <v>91937</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,19 +788,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -814,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492771</v>
+        <v>492932</v>
       </c>
       <c r="R3" t="n">
-        <v>7144199</v>
+        <v>7144160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029146</v>
+        <v>122743277</v>
       </c>
       <c r="B4" t="n">
-        <v>80124</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -892,34 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skiddammtjärnen, Skiddammtjärnen, Jmt</t>
+          <t>Gräningen SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493010</v>
+        <v>492763</v>
       </c>
       <c r="R4" t="n">
-        <v>7144126</v>
+        <v>7144294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,31 +963,30 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gles, gammal grannaturskog/gransumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127028941</v>
+        <v>127028985</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492956</v>
+        <v>492980</v>
       </c>
       <c r="R5" t="n">
-        <v>7144106</v>
+        <v>7144133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028985</v>
+        <v>127029404</v>
       </c>
       <c r="B6" t="n">
-        <v>82861</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492980</v>
+        <v>493031</v>
       </c>
       <c r="R6" t="n">
-        <v>7144133</v>
+        <v>7144153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127029012</v>
+        <v>127029146</v>
       </c>
       <c r="B7" t="n">
-        <v>75144</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492980</v>
+        <v>493010</v>
       </c>
       <c r="R7" t="n">
-        <v>7144133</v>
+        <v>7144126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127029337</v>
+        <v>127028941</v>
       </c>
       <c r="B8" t="n">
-        <v>91356</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493018</v>
+        <v>492956</v>
       </c>
       <c r="R8" t="n">
-        <v>7144127</v>
+        <v>7144106</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127029103</v>
+        <v>127029012</v>
       </c>
       <c r="B9" t="n">
-        <v>79101</v>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492989</v>
+        <v>492980</v>
       </c>
       <c r="R9" t="n">
         <v>7144133</v>
@@ -1490,108 +1490,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>127029404</v>
-      </c>
-      <c r="B10" t="n">
-        <v>82861</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Skiddammtjärnen, Skiddammtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>493031</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7144153</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gles, gammal grannaturskog/gransumpskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29495-2024 artfynd.xlsx
+++ b/artfynd/A 29495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029103</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743277</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028985</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029404</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029146</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028941</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,8 +1530,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029012</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>